--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1609-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1609-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09479A51-2FD6-4994-93F4-04D022E6F576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E52674CD-2FDE-4081-8067-4D7D07FFB1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{331EEB78-ADE9-4016-8FF9-5C5A99284155}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{60A57A9C-D88A-47A7-B99C-696099984C7D}"/>
   </bookViews>
   <sheets>
     <sheet name="1609-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1562,27 +1562,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D8FB833-E7F1-460A-9536-7BC18C3B56D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D727FFD-8ADA-4B41-A0C8-BE95B6CF7CA1}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1616,7 +1615,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1652,7 +1651,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1704,7 +1703,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1772,7 +1771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1844,7 +1843,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1916,7 +1915,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1988,7 +1987,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2204,7 +2203,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="41">
         <v>2018</v>
       </c>
@@ -2276,7 +2275,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="43"/>
       <c r="B12" s="44"/>
       <c r="C12" s="18" t="s">
@@ -2304,7 +2303,7 @@
       <c r="W12" s="50"/>
       <c r="X12" s="46"/>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2017</v>
       </c>
@@ -2376,7 +2375,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2016</v>
       </c>
@@ -2448,7 +2447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2015</v>
       </c>
@@ -2520,7 +2519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2014</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2013</v>
       </c>
@@ -2664,7 +2663,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2736,7 +2735,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2011</v>
       </c>
@@ -2808,7 +2807,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2880,7 +2879,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2009</v>
       </c>
@@ -2952,7 +2951,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2008</v>
       </c>
@@ -3024,7 +3023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="51">
         <v>2007</v>
       </c>
@@ -3096,7 +3095,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="53"/>
       <c r="B24" s="54"/>
       <c r="C24" s="20" t="s">
@@ -3124,7 +3123,7 @@
       <c r="W24" s="60"/>
       <c r="X24" s="56"/>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2006</v>
       </c>
@@ -3196,7 +3195,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2005</v>
       </c>
@@ -3268,7 +3267,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2004</v>
       </c>
@@ -3340,7 +3339,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2003</v>
       </c>
@@ -3412,7 +3411,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2002</v>
       </c>
@@ -3484,7 +3483,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2001</v>
       </c>
@@ -3556,7 +3555,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2000</v>
       </c>
@@ -3628,7 +3627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>1999</v>
       </c>
@@ -3700,7 +3699,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1998</v>
       </c>
@@ -3772,7 +3771,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1997</v>
       </c>
@@ -3844,7 +3843,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>1996</v>
       </c>
@@ -3916,7 +3915,7 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1995</v>
       </c>
@@ -3988,7 +3987,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1994</v>
       </c>
@@ -4060,7 +4059,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>1993</v>
       </c>
@@ -4132,7 +4131,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1992</v>
       </c>
@@ -4204,7 +4203,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>1991</v>
       </c>
@@ -4276,7 +4275,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1990</v>
       </c>
@@ -4348,7 +4347,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="51">
         <v>1989</v>
       </c>
@@ -4420,7 +4419,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="53"/>
       <c r="B43" s="54"/>
       <c r="C43" s="20" t="s">
@@ -4448,7 +4447,7 @@
       <c r="W43" s="60"/>
       <c r="X43" s="56"/>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>1988</v>
       </c>
@@ -4520,7 +4519,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>1986</v>
       </c>
@@ -4592,7 +4591,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>1983</v>
       </c>
@@ -4664,7 +4663,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39" t="s">
         <v>56</v>
       </c>
